--- a/data/trans_camb/IP1009-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1009-Estudios-trans_camb.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,65</t>
+          <t>0,0; 3,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,92</t>
+          <t>0,0; 1,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -792,27 +792,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 0,94</t>
+          <t>-0,11; 1,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 0,11</t>
+          <t>-1,02; 0,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 0,85</t>
+          <t>-0,52; 0,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 0,13</t>
+          <t>-0,55; 0,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 0,6</t>
+          <t>-0,26; 0,65</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-68,24; 533,55</t>
+          <t>-71,65; 561,76</t>
         </is>
       </c>
     </row>
@@ -943,12 +943,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 0,0</t>
+          <t>-2,03; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 1,33</t>
+          <t>-0,73; 1,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -963,12 +963,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 0,0</t>
+          <t>-1,28; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,66</t>
+          <t>-0,38; 0,64</t>
         </is>
       </c>
     </row>
@@ -1099,22 +1099,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 0,4</t>
+          <t>-0,26; 0,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 0,75</t>
+          <t>-0,14; 0,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 0,08</t>
+          <t>-0,68; 0,07</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 0,61</t>
+          <t>-0,39; 0,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 0,51</t>
+          <t>-0,14; 0,49</t>
         </is>
       </c>
     </row>
@@ -1190,17 +1190,17 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 238,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-49,86; 551,66</t>
+          <t>-52,81; 514,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1009-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1009-Estudios-trans_camb.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,97</t>
+          <t>0,0; 3,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 0,57</t>
+          <t>-0,22; 0,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 1,01</t>
+          <t>-0,09; 1,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 0,11</t>
+          <t>-1,02; 0,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 0,86</t>
+          <t>-0,6; 0,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 0,17</t>
+          <t>-0,5; 0,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 0,65</t>
+          <t>-0,24; 0,63</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-85,47; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-71,65; 561,76</t>
+          <t>-68,75; 611,82</t>
         </is>
       </c>
     </row>
@@ -943,12 +943,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 0,0</t>
+          <t>-1,48; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 1,43</t>
+          <t>-0,74; 1,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 0,0</t>
+          <t>-1,21; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 0,44</t>
+          <t>-0,26; 0,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 0,7</t>
+          <t>-0,15; 0,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 0,07</t>
+          <t>-0,76; 0,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 0,53</t>
+          <t>-0,39; 0,56</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 0,14</t>
+          <t>-0,35; 0,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 0,49</t>
+          <t>-0,14; 0,52</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-52,81; 514,58</t>
+          <t>-55,4; 684,35</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1009-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1009-Estudios-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,17 +593,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0,72</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,9</t>
+          <t>0,0; 1,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -669,17 +669,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,31</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,12</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,03</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>0,28</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,31</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,12</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 0,56</t>
+          <t>-1,08; 0,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 1,06</t>
+          <t>-0,59; 0,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 0,13</t>
+          <t>-0,22; 0,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 0,95</t>
+          <t>-0,11; 0,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,18</t>
+          <t>-0,54; 0,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 0,63</t>
+          <t>-0,24; 0,6</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-71,03%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>27,31%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>31,66%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>260,37%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-71,03%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>27,31%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-85,47; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-68,75; 611,82</t>
+          <t>-68,24; 533,55</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>-0,36</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>0,07</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 1,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,01; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,73; 1,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 0,0</t>
+          <t>-0,99; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,64</t>
+          <t>-0,38; 0,66</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>19,76%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,08</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0,03</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>0,21</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,2</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,08</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 0,37</t>
+          <t>-0,71; 0,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 0,72</t>
+          <t>-0,39; 0,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 0,08</t>
+          <t>-0,28; 0,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 0,56</t>
+          <t>-0,15; 0,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 0,13</t>
+          <t>-0,36; 0,14</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 0,52</t>
+          <t>-0,14; 0,51</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-71,12%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>26,44%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>16,05%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>131,08%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-71,12%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>26,44%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 238,02</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-55,4; 684,35</t>
+          <t>-49,86; 551,66</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1009-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1009-Estudios-trans_camb.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -118,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -131,6 +134,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -497,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -591,467 +600,255 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,72</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,38</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.7242325649610405</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0.3793567161028486</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,65</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,92</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="n">
+        <v>3.650523858811947</v>
+      </c>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="n">
+        <v>1.917098080693348</v>
+      </c>
+      <c r="H6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="6" t="inlineStr"/>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-0,31</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,12</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,03</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,28</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-0,15</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,19</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr"/>
+      <c r="D8" s="6" t="inlineStr"/>
+      <c r="E8" s="6" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-1,08; 0,11</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-0,59; 0,85</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-0,22; 0,57</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-0,11; 0,94</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-0,54; 0,13</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-0,24; 0,6</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr"/>
+      <c r="D9" s="6" t="inlineStr"/>
+      <c r="E9" s="6" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n"/>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-71,03%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>27,31%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>31,66%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>260,37%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-52,71%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>67,24%</t>
-        </is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>-0.308502456195374</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.1186075257557663</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.03408056029558237</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.2802284289400925</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-0.1487102969485662</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>0.1896913063128699</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-68,24; 533,55</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-1.076857151647629</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-0.5937194083046824</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-0.2160488184980638</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-0.1113605051455228</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-0.5380057917742336</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-0.2375134153952134</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,36</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,07</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-0,19</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,02</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.1097252151125817</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.8484786584357057</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.5676107290571091</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0.9422080238626328</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0.1273991917023953</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>0.6041436202484624</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-2,01; 0,0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-0,73; 1,33</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-0,99; 0,0</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-0,38; 0,66</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>-0.7103325599067823</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0.273096002000539</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0.3166498118504727</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>2.603662572722898</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.5271420250134426</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.672409788622748</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>19,76%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>9,58%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr"/>
+      <c r="D14" s="6" t="inlineStr"/>
+      <c r="E14" s="6" t="inlineStr"/>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="n">
+        <v>-0.6824109442993241</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr"/>
+      <c r="D15" s="6" t="inlineStr"/>
+      <c r="E15" s="6" t="inlineStr"/>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="n">
+        <v>5.335509869413306</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1059,153 +856,265 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-0,2</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>0,08</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,03</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,21</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,09</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,14</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.3640236141292065</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.07192035774648649</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>-0.1907386403339006</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>0.01828177079494283</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-0,71; 0,08</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-0,39; 0,61</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-0,28; 0,4</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-0,15; 0,75</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-0,36; 0,14</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-0,14; 0,51</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="n">
+        <v>-2.014093474407538</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-0.7298843554146108</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-0.987925631967123</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-0.3829798978624566</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>-71,12%</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>26,44%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>16,05%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>131,08%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-41,19%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>62,33%</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>1.32818862833194</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>0.6553279649096239</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 238,02</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-49,86; 551,66</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr"/>
+      <c r="D19" s="6" t="inlineStr"/>
+      <c r="E19" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>0.1975705832121074</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0.09584723243774508</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr"/>
+      <c r="D20" s="6" t="inlineStr"/>
+      <c r="E20" s="6" t="inlineStr"/>
+      <c r="F20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr"/>
+      <c r="D21" s="6" t="inlineStr"/>
+      <c r="E21" s="6" t="inlineStr"/>
+      <c r="F21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-0.2040647041273624</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>0.07586267547868351</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0.02548202975772636</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0.2081494542439439</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-0.09257592253269768</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>0.1400779988597358</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-0.7139943753346053</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-0.3883709377094584</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-0.2796929392974818</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-0.153221505012571</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-0.355874938478019</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-0.1366657259835838</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0.08295417460884068</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0.6087266283170326</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0.3964377093092417</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0.7501968086531752</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.1444624892017564</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>0.5059797723764051</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n"/>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>-0.7111845575237357</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>0.2643885111028369</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>0.1604646666333718</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>1.310752444084459</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-0.4119263486650951</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>0.6232918562407428</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr"/>
+      <c r="D26" s="6" t="inlineStr"/>
+      <c r="E26" s="6" t="inlineStr"/>
+      <c r="F26" s="6" t="inlineStr"/>
+      <c r="G26" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.4985624115231074</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr"/>
+      <c r="D27" s="6" t="inlineStr"/>
+      <c r="E27" s="6" t="inlineStr"/>
+      <c r="F27" s="6" t="inlineStr"/>
+      <c r="G27" s="6" t="n">
+        <v>2.380152336554186</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>5.516579444030122</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1213,14 +1122,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A22:A27"/>
+    <mergeCell ref="A4:A9"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="A10:A15"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
